--- a/evac_by_zip/evac_by_zip_2026-07-30.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-07-30.xlsx
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>91</v>
@@ -849,7 +849,7 @@
         <v>136</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F145" s="19" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="G145" s="19" t="n">
